--- a/PaperImplementationPlan.xlsx
+++ b/PaperImplementationPlan.xlsx
@@ -1,24 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="27809"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/LiuFangGuo/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shaishai\Desktop\11.5\123\TEMPpaper\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="660" yWindow="460" windowWidth="27320" windowHeight="14820" tabRatio="500"/>
+    <workbookView xWindow="660" yWindow="465" windowWidth="27315" windowHeight="14820" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="2018-31-stage" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="150001" concurrentCalc="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
-      <x14:workbookPr defaultImageDpi="32767"/>
-    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -27,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>日期</t>
   </si>
@@ -113,15 +110,32 @@
     <t>日记反省</t>
   </si>
   <si>
-    <t>完成实施计划表的能完成的部分
-每天两个小时是这么规划的：
-切割成25+5=30分钟的最小任务，集中精力，完成突破</t>
+    <t>1.完成资料查找验证：现在离开学校查找资料的VPN没找到，学校图书馆这边没有可以用的VPN，有一个系统可以帮助查找资料，经过测试，从其他地方可以登录，但是资料的查找的及时性有待考证，这个原因在于资料的获得依赖于其他学校图书馆，因为目前没有得到理想的反馈；                                                                          2.下载了4篇内容相关的论文，对于其中内容的相关性需要进一步阅读论文才能得出结论；</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.对下载的4篇论文的内容进行梳理；                   2.了解卷积神经网络和交通流量等和论文相关的知识；                                                                  3.希望可以得出一个前期的研究思路，并对于后期的工作进行更加具体的规划；</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.今天完成的内容还未涉及和论文相关的实质性内容，只是完成了一些前期的工作准备，需要有更加整体的思路；</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
       <t>目标：论文初稿完成
 题目：基于卷积神经网络的交通流量预测
 时间投入：一共35天，5周，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每天保障</t>
     </r>
     <r>
       <rPr>
@@ -129,13 +143,23 @@
         <color rgb="FFFF0000"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>每天保障2个小时</t>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个小时</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="DengXian"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -147,10 +171,21 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>项目地址：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
-      <t>项目地址：git@github.com:GuoLiuFang/TEMPpaper.git</t>
-    </r>
+      <t>git@github.com:GuoLiuFang/TEMPpaper.git</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -158,20 +193,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -179,7 +214,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -187,7 +222,7 @@
       <u/>
       <sz val="12"/>
       <color theme="11"/>
-      <name val="Calibri"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -195,6 +230,32 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="DengXian"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="DengXian"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="DengXian"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -233,28 +294,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -264,23 +328,26 @@
     </xf>
   </cellXfs>
   <cellStyles count="11">
-    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="9" builtinId="8" hidden="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="超链接" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="超链接" xfId="5" builtinId="8" hidden="1"/>
+    <cellStyle name="超链接" xfId="7" builtinId="8" hidden="1"/>
+    <cellStyle name="超链接" xfId="9" builtinId="8" hidden="1"/>
+    <cellStyle name="已访问的超链接" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="已访问的超链接" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="已访问的超链接" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="已访问的超链接" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="已访问的超链接" xfId="10" builtinId="9" hidden="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -550,18 +617,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AF36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="59.5" customWidth="1"/>
     <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.375" customWidth="1"/>
+    <col min="4" max="4" width="24.625" customWidth="1"/>
     <col min="7" max="7" width="38.5" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="30.875" customWidth="1"/>
+    <col min="9" max="9" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -659,17 +726,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:32" s="2" customFormat="1" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="3">
+    <row r="2" spans="1:32" s="2" customFormat="1" ht="154.5" customHeight="1">
+      <c r="A2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="8">
         <v>1</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="8">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1">
@@ -678,31 +745,34 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="H2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" s="2" customFormat="1" ht="78.75">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
       <c r="E3" s="1">
         <v>43123</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
       </c>
-      <c r="G3" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="G3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:32" s="2" customFormat="1">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
       <c r="E4" s="1">
         <v>43124</v>
       </c>
@@ -713,11 +783,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+    <row r="5" spans="1:32" s="2" customFormat="1">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="1">
         <v>43125</v>
       </c>
@@ -728,11 +798,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+    <row r="6" spans="1:32" s="2" customFormat="1">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="1">
         <v>43126</v>
       </c>
@@ -743,11 +813,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+    <row r="7" spans="1:32" s="2" customFormat="1">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
       <c r="E7" s="1">
         <v>43127</v>
       </c>
@@ -758,11 +828,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+    <row r="8" spans="1:32" s="2" customFormat="1">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
       <c r="E8" s="1">
         <v>43128</v>
       </c>
@@ -773,11 +843,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="8" t="s">
+    <row r="9" spans="1:32" s="2" customFormat="1">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="9" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="1">
@@ -790,11 +860,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="9"/>
+    <row r="10" spans="1:32" s="2" customFormat="1">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="1">
         <v>43130</v>
       </c>
@@ -805,11 +875,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="9"/>
+    <row r="11" spans="1:32" s="2" customFormat="1">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="1">
         <v>43131</v>
       </c>
@@ -820,11 +890,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="9"/>
+    <row r="12" spans="1:32" s="2" customFormat="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="1">
         <v>43132</v>
       </c>
@@ -835,11 +905,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="9"/>
+    <row r="13" spans="1:32" s="2" customFormat="1">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="1">
         <v>43133</v>
       </c>
@@ -850,11 +920,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="9"/>
+    <row r="14" spans="1:32" s="2" customFormat="1">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="1">
         <v>43134</v>
       </c>
@@ -865,11 +935,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="9"/>
+    <row r="15" spans="1:32" s="2" customFormat="1">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="1">
         <v>43135</v>
       </c>
@@ -880,13 +950,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3">
+    <row r="16" spans="1:32" s="2" customFormat="1">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8">
         <v>3</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>6</v>
       </c>
       <c r="E16" s="1">
@@ -899,11 +969,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+    <row r="17" spans="1:7" s="2" customFormat="1">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="1">
         <v>43137</v>
       </c>
@@ -914,11 +984,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+    <row r="18" spans="1:7" s="2" customFormat="1">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
       <c r="E18" s="1">
         <v>43138</v>
       </c>
@@ -929,11 +999,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+    <row r="19" spans="1:7" s="2" customFormat="1">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="1">
         <v>43139</v>
       </c>
@@ -944,11 +1014,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+    <row r="20" spans="1:7" s="2" customFormat="1">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
       <c r="E20" s="1">
         <v>43140</v>
       </c>
@@ -959,11 +1029,11 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+    <row r="21" spans="1:7" s="2" customFormat="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
       <c r="E21" s="1">
         <v>43141</v>
       </c>
@@ -974,11 +1044,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+    <row r="22" spans="1:7" s="2" customFormat="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
       <c r="E22" s="1">
         <v>43142</v>
       </c>
@@ -989,14 +1059,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3">
+    <row r="23" spans="1:7" s="2" customFormat="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8">
         <v>7</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="3">
         <v>43143</v>
       </c>
       <c r="F23" s="2">
@@ -1006,12 +1076,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="6">
+    <row r="24" spans="1:7" s="2" customFormat="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="3">
         <v>43144</v>
       </c>
       <c r="F24" s="2">
@@ -1021,12 +1091,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="6">
+    <row r="25" spans="1:7" s="2" customFormat="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="3">
         <v>43145</v>
       </c>
       <c r="F25" s="2">
@@ -1036,12 +1106,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="6">
+    <row r="26" spans="1:7" s="2" customFormat="1">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="3">
         <v>43146</v>
       </c>
       <c r="F26" s="2">
@@ -1051,12 +1121,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="6">
+    <row r="27" spans="1:7" s="2" customFormat="1">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="3">
         <v>43147</v>
       </c>
       <c r="F27" s="2">
@@ -1066,12 +1136,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="6">
+    <row r="28" spans="1:7" s="2" customFormat="1">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="3">
         <v>43148</v>
       </c>
       <c r="F28" s="2">
@@ -1081,12 +1151,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="6">
+    <row r="29" spans="1:7" s="2" customFormat="1">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="3">
         <v>43149</v>
       </c>
       <c r="F29" s="2">
@@ -1096,18 +1166,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3"/>
-      <c r="B30" s="4" t="s">
+    <row r="30" spans="1:7" s="2" customFormat="1">
+      <c r="A30" s="8"/>
+      <c r="B30" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="3">
         <v>43150</v>
       </c>
       <c r="F30" s="2">
@@ -1117,12 +1187,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="6">
+    <row r="31" spans="1:7" s="2" customFormat="1">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="3">
         <v>43151</v>
       </c>
       <c r="F31" s="2">
@@ -1132,12 +1202,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="6">
+    <row r="32" spans="1:7" s="2" customFormat="1">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="3">
         <v>43152</v>
       </c>
       <c r="F32" s="2">
@@ -1147,12 +1217,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="6">
+    <row r="33" spans="1:7" s="2" customFormat="1">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="3">
         <v>43153</v>
       </c>
       <c r="F33" s="2">
@@ -1162,11 +1232,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+    <row r="34" spans="1:7" s="2" customFormat="1">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
       <c r="E34" s="1">
         <v>43154</v>
       </c>
@@ -1177,11 +1247,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+    <row r="35" spans="1:7" s="2" customFormat="1">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
       <c r="E35" s="1">
         <v>43155</v>
       </c>
@@ -1192,11 +1262,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+    <row r="36" spans="1:7" s="2" customFormat="1">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
       <c r="E36" s="1">
         <v>43156</v>
       </c>
@@ -1221,7 +1291,8 @@
     <mergeCell ref="B30:B36"/>
     <mergeCell ref="C30:C36"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>